--- a/input/validation_statistics.xlsx
+++ b/input/validation_statistics.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10201"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Sonnewald/GitHub/SimPaths/input/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\andy_local\SimPaths project files\SimPaths\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F2C890B-212E-4B45-BD48-40AD02256F73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3C23905-C524-4B69-AE8F-A6215B6AA65D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="680" windowWidth="29660" windowHeight="17800" tabRatio="839" firstSheet="21" activeTab="27" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="839" firstSheet="22" activeTab="29" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="studentsByAge" sheetId="1" r:id="rId1"/>
@@ -41,13 +41,15 @@
     <sheet name="lifeSatisfactionByAgeGroup" sheetId="56" r:id="rId26"/>
     <sheet name="healthMCSByAgeGroup" sheetId="57" r:id="rId27"/>
     <sheet name="healthPCSByAgeGroup" sheetId="58" r:id="rId28"/>
+    <sheet name="benefitsUC" sheetId="59" r:id="rId29"/>
+    <sheet name="benefitsNonUC" sheetId="60" r:id="rId30"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="361" uniqueCount="278">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="365" uniqueCount="279">
   <si>
     <t>Year</t>
   </si>
@@ -881,13 +883,16 @@
   </si>
   <si>
     <t>health_pcs_score_male_80_100</t>
+  </si>
+  <si>
+    <t>All</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -896,6 +901,10 @@
       <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="2">
@@ -922,19 +931,23 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1"/>
     <xf numFmtId="1" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="2"/>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="1" xfId="2" applyNumberFormat="1"/>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{F36E4FC5-7866-43FC-907D-3547C8EA8E68}"/>
+    <cellStyle name="Normal 3" xfId="2" xr:uid="{2C2E85C3-8BFB-4F65-9B4D-5C7468A54BDC}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1267,9 +1280,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K12"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1304,7 +1317,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>2021</v>
       </c>
@@ -1339,7 +1352,7 @@
         <v>0.17187501490116119</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>2020</v>
       </c>
@@ -1374,7 +1387,7 @@
         <v>0.17955547571182251</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>2019</v>
       </c>
@@ -1409,7 +1422,7 @@
         <v>0.19602103531360626</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>2018</v>
       </c>
@@ -1444,7 +1457,7 @@
         <v>0.20747773349285126</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>2017</v>
       </c>
@@ -1479,7 +1492,7 @@
         <v>0.21695126593112946</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>2016</v>
       </c>
@@ -1514,7 +1527,7 @@
         <v>0.22391675412654877</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>2015</v>
       </c>
@@ -1549,7 +1562,7 @@
         <v>0.22631487250328064</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>2014</v>
       </c>
@@ -1584,7 +1597,7 @@
         <v>0.23363189399242401</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>2013</v>
       </c>
@@ -1619,7 +1632,7 @@
         <v>0.23988360166549683</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>2012</v>
       </c>
@@ -1654,7 +1667,7 @@
         <v>0.24267652630805969</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>2011</v>
       </c>
@@ -1697,9 +1710,9 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:G12"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1722,7 +1735,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>2021</v>
       </c>
@@ -1745,7 +1758,7 @@
         <v>2.898453950881958</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>2020</v>
       </c>
@@ -1768,7 +1781,7 @@
         <v>2.8711950778961182</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>2019</v>
       </c>
@@ -1791,7 +1804,7 @@
         <v>2.8905754089355469</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>2018</v>
       </c>
@@ -1814,7 +1827,7 @@
         <v>2.9101502895355225</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>2017</v>
       </c>
@@ -1837,7 +1850,7 @@
         <v>2.9035961627960205</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>2016</v>
       </c>
@@ -1860,7 +1873,7 @@
         <v>2.8773038387298584</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>2015</v>
       </c>
@@ -1883,7 +1896,7 @@
         <v>2.8834474086761475</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>2014</v>
       </c>
@@ -1906,7 +1919,7 @@
         <v>2.8930943012237549</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>2013</v>
       </c>
@@ -1929,7 +1942,7 @@
         <v>2.9139957427978516</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>2012</v>
       </c>
@@ -1952,7 +1965,7 @@
         <v>2.9485378265380859</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>2011</v>
       </c>
@@ -1983,9 +1996,9 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1:S12"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2044,7 +2057,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>2021</v>
       </c>
@@ -2103,7 +2116,7 @@
         <v>9.9496917724609375</v>
       </c>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>2020</v>
       </c>
@@ -2162,7 +2175,7 @@
         <v>10.116863250732422</v>
       </c>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>2019</v>
       </c>
@@ -2221,7 +2234,7 @@
         <v>9.8415822982788086</v>
       </c>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>2018</v>
       </c>
@@ -2280,7 +2293,7 @@
         <v>9.9166078567504883</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>2017</v>
       </c>
@@ -2339,7 +2352,7 @@
         <v>10.06915283203125</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>2016</v>
       </c>
@@ -2398,7 +2411,7 @@
         <v>10.155402183532715</v>
       </c>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>2015</v>
       </c>
@@ -2457,7 +2470,7 @@
         <v>9.7329807281494141</v>
       </c>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>2014</v>
       </c>
@@ -2516,7 +2529,7 @@
         <v>9.9710407257080078</v>
       </c>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>2013</v>
       </c>
@@ -2566,7 +2579,7 @@
         <v>10.67141056060791</v>
       </c>
       <c r="Q10" s="1">
-        <v>9.6772537231445312</v>
+        <v>9.6772537231445313</v>
       </c>
       <c r="R10" s="1">
         <v>10.73939323425293</v>
@@ -2575,7 +2588,7 @@
         <v>9.5084981918334961</v>
       </c>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>2012</v>
       </c>
@@ -2634,7 +2647,7 @@
         <v>9.566375732421875</v>
       </c>
     </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>2011</v>
       </c>
@@ -2684,7 +2697,7 @@
         <v>10.881806373596191</v>
       </c>
       <c r="Q12" s="1">
-        <v>9.8155288696289062</v>
+        <v>9.8155288696289063</v>
       </c>
       <c r="R12" s="1">
         <v>10.733816146850586</v>
@@ -2701,9 +2714,9 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <dimension ref="A1:S12"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2762,7 +2775,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>2021</v>
       </c>
@@ -2821,7 +2834,7 @@
         <v>0.11799130588769913</v>
       </c>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>2020</v>
       </c>
@@ -2880,7 +2893,7 @@
         <v>0.13460986316204071</v>
       </c>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>2019</v>
       </c>
@@ -2939,7 +2952,7 @@
         <v>0.10989783704280853</v>
       </c>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>2018</v>
       </c>
@@ -2998,7 +3011,7 @@
         <v>0.12090980261564255</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>2017</v>
       </c>
@@ -3057,7 +3070,7 @@
         <v>0.12992607057094574</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>2016</v>
       </c>
@@ -3116,7 +3129,7 @@
         <v>0.14206910133361816</v>
       </c>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>2015</v>
       </c>
@@ -3175,7 +3188,7 @@
         <v>0.10126698017120361</v>
       </c>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>2014</v>
       </c>
@@ -3234,7 +3247,7 @@
         <v>0.11174842715263367</v>
       </c>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>2013</v>
       </c>
@@ -3245,7 +3258,7 @@
         <v>0</v>
       </c>
       <c r="D10" s="1">
-        <v>0.11592483520507812</v>
+        <v>0.11592483520507813</v>
       </c>
       <c r="E10" s="1">
         <v>6.5038792788982391E-2</v>
@@ -3293,7 +3306,7 @@
         <v>8.1463396549224854E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>2012</v>
       </c>
@@ -3352,7 +3365,7 @@
         <v>8.6762040853500366E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>2011</v>
       </c>
@@ -3419,9 +3432,9 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <dimension ref="A1:S12"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -3480,7 +3493,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>2021</v>
       </c>
@@ -3539,7 +3552,7 @@
         <v>0.11782421171665192</v>
       </c>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>2020</v>
       </c>
@@ -3598,7 +3611,7 @@
         <v>0.13834667205810547</v>
       </c>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>2019</v>
       </c>
@@ -3657,7 +3670,7 @@
         <v>0.11367066949605942</v>
       </c>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>2018</v>
       </c>
@@ -3716,7 +3729,7 @@
         <v>0.13104404509067535</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>2017</v>
       </c>
@@ -3775,7 +3788,7 @@
         <v>0.14412355422973633</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>2016</v>
       </c>
@@ -3834,7 +3847,7 @@
         <v>0.18427404761314392</v>
       </c>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>2015</v>
       </c>
@@ -3893,7 +3906,7 @@
         <v>0.10914843529462814</v>
       </c>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>2014</v>
       </c>
@@ -3952,7 +3965,7 @@
         <v>0.1080840602517128</v>
       </c>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>2013</v>
       </c>
@@ -4011,7 +4024,7 @@
         <v>6.923229992389679E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>2012</v>
       </c>
@@ -4070,7 +4083,7 @@
         <v>7.6862581074237823E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>2011</v>
       </c>
@@ -4137,9 +4150,9 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
   <dimension ref="A1:S12"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -4198,7 +4211,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>2021</v>
       </c>
@@ -4257,7 +4270,7 @@
         <v>0.10535970330238342</v>
       </c>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>2020</v>
       </c>
@@ -4316,7 +4329,7 @@
         <v>0.10505391657352448</v>
       </c>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>2019</v>
       </c>
@@ -4375,7 +4388,7 @@
         <v>8.543127030134201E-2</v>
       </c>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>2018</v>
       </c>
@@ -4434,7 +4447,7 @@
         <v>9.830726683139801E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>2017</v>
       </c>
@@ -4493,7 +4506,7 @@
         <v>9.3566030263900757E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>2016</v>
       </c>
@@ -4552,7 +4565,7 @@
         <v>0.10398537665605545</v>
       </c>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>2015</v>
       </c>
@@ -4611,7 +4624,7 @@
         <v>9.9448680877685547E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>2014</v>
       </c>
@@ -4670,7 +4683,7 @@
         <v>0.13332265615463257</v>
       </c>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>2013</v>
       </c>
@@ -4729,7 +4742,7 @@
         <v>0.11196029931306839</v>
       </c>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>2012</v>
       </c>
@@ -4788,7 +4801,7 @@
         <v>9.9097676575183868E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>2011</v>
       </c>
@@ -4855,9 +4868,9 @@
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
   <dimension ref="A1:S12"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -4916,7 +4929,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>2021</v>
       </c>
@@ -4975,7 +4988,7 @@
         <v>0.13727535307407379</v>
       </c>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>2020</v>
       </c>
@@ -5034,7 +5047,7 @@
         <v>0.17250306904315948</v>
       </c>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>2019</v>
       </c>
@@ -5093,7 +5106,7 @@
         <v>0.14163240790367126</v>
       </c>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>2018</v>
       </c>
@@ -5152,7 +5165,7 @@
         <v>0.13500732183456421</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>2017</v>
       </c>
@@ -5211,7 +5224,7 @@
         <v>0.15256033837795258</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>2016</v>
       </c>
@@ -5270,7 +5283,7 @@
         <v>8.7829440832138062E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>2015</v>
       </c>
@@ -5329,7 +5342,7 @@
         <v>7.7023454010486603E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>2014</v>
       </c>
@@ -5388,7 +5401,7 @@
         <v>8.3866730332374573E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>2013</v>
       </c>
@@ -5447,7 +5460,7 @@
         <v>6.8383723497390747E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>2012</v>
       </c>
@@ -5506,7 +5519,7 @@
         <v>0.10309414565563202</v>
       </c>
     </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>2011</v>
       </c>
@@ -5573,9 +5586,9 @@
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0F00-000000000000}">
   <dimension ref="A1:C12"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -5586,7 +5599,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>2021</v>
       </c>
@@ -5597,7 +5610,7 @@
         <v>0.77519410848617554</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>2020</v>
       </c>
@@ -5608,7 +5621,7 @@
         <v>0.77731060981750488</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>2019</v>
       </c>
@@ -5619,7 +5632,7 @@
         <v>0.7874070405960083</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>2018</v>
       </c>
@@ -5630,7 +5643,7 @@
         <v>0.78019678592681885</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>2017</v>
       </c>
@@ -5641,7 +5654,7 @@
         <v>0.78231054544448853</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>2016</v>
       </c>
@@ -5652,7 +5665,7 @@
         <v>0.78842121362686157</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>2015</v>
       </c>
@@ -5663,7 +5676,7 @@
         <v>0.78793185949325562</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>2014</v>
       </c>
@@ -5674,7 +5687,7 @@
         <v>0.78220373392105103</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>2013</v>
       </c>
@@ -5685,7 +5698,7 @@
         <v>0.77125352621078491</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>2012</v>
       </c>
@@ -5696,7 +5709,7 @@
         <v>0.76128304004669189</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>2011</v>
       </c>
@@ -5715,9 +5728,9 @@
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1000-000000000000}">
   <dimension ref="A1:S12"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -5776,7 +5789,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>2021</v>
       </c>
@@ -5835,7 +5848,7 @@
         <v>7.8269904479384422E-3</v>
       </c>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>2020</v>
       </c>
@@ -5894,7 +5907,7 @@
         <v>1.3787235133349895E-2</v>
       </c>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>2019</v>
       </c>
@@ -5953,7 +5966,7 @@
         <v>7.2737107984721661E-3</v>
       </c>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>2018</v>
       </c>
@@ -6012,7 +6025,7 @@
         <v>1.2163837440311909E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>2017</v>
       </c>
@@ -6071,7 +6084,7 @@
         <v>1.2493204325437546E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>2016</v>
       </c>
@@ -6130,7 +6143,7 @@
         <v>1.333949901163578E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>2015</v>
       </c>
@@ -6189,7 +6202,7 @@
         <v>1.5667887404561043E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>2014</v>
       </c>
@@ -6248,7 +6261,7 @@
         <v>1.1592219583690166E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>2013</v>
       </c>
@@ -6307,7 +6320,7 @@
         <v>7.7026672661304474E-3</v>
       </c>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>2012</v>
       </c>
@@ -6366,7 +6379,7 @@
         <v>5.9830662794411182E-3</v>
       </c>
     </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>2011</v>
       </c>
@@ -6433,9 +6446,9 @@
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1100-000000000000}">
   <dimension ref="A1:D12"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -6449,7 +6462,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>2021</v>
       </c>
@@ -6463,7 +6476,7 @@
         <v>0.68726056814193726</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>2020</v>
       </c>
@@ -6477,7 +6490,7 @@
         <v>0.67925095558166504</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>2019</v>
       </c>
@@ -6491,7 +6504,7 @@
         <v>0.6856042742729187</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>2018</v>
       </c>
@@ -6505,7 +6518,7 @@
         <v>0.67521584033966064</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>2017</v>
       </c>
@@ -6519,7 +6532,7 @@
         <v>0.67329293489456177</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>2016</v>
       </c>
@@ -6533,7 +6546,7 @@
         <v>0.67869198322296143</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>2015</v>
       </c>
@@ -6547,7 +6560,7 @@
         <v>0.66872549057006836</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>2014</v>
       </c>
@@ -6561,7 +6574,7 @@
         <v>0.67186468839645386</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>2013</v>
       </c>
@@ -6575,7 +6588,7 @@
         <v>0.66411858797073364</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>2012</v>
       </c>
@@ -6589,7 +6602,7 @@
         <v>0.64968019723892212</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>2011</v>
       </c>
@@ -6611,9 +6624,9 @@
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1200-000000000000}">
   <dimension ref="A1:Y12"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -6690,7 +6703,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>2021</v>
       </c>
@@ -6767,7 +6780,7 @@
         <v>0.75348234176635742</v>
       </c>
     </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>2020</v>
       </c>
@@ -6844,7 +6857,7 @@
         <v>0.69421589374542236</v>
       </c>
     </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>2019</v>
       </c>
@@ -6921,7 +6934,7 @@
         <v>0.72084945440292358</v>
       </c>
     </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>2018</v>
       </c>
@@ -6998,7 +7011,7 @@
         <v>0.72034323215484619</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>2017</v>
       </c>
@@ -7075,7 +7088,7 @@
         <v>0.70522725582122803</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>2016</v>
       </c>
@@ -7152,7 +7165,7 @@
         <v>0.72512173652648926</v>
       </c>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>2015</v>
       </c>
@@ -7229,7 +7242,7 @@
         <v>0.7023894190788269</v>
       </c>
     </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>2014</v>
       </c>
@@ -7306,7 +7319,7 @@
         <v>0.67400050163269043</v>
       </c>
     </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>2013</v>
       </c>
@@ -7383,7 +7396,7 @@
         <v>0.67601567506790161</v>
       </c>
     </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>2012</v>
       </c>
@@ -7460,7 +7473,7 @@
         <v>0.69270336627960205</v>
       </c>
     </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>2011</v>
       </c>
@@ -7545,9 +7558,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:N12"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -7591,7 +7604,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>2021</v>
       </c>
@@ -7635,7 +7648,7 @@
         <v>0.17187501490116119</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>2020</v>
       </c>
@@ -7679,7 +7692,7 @@
         <v>0.17955547571182251</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>2019</v>
       </c>
@@ -7723,7 +7736,7 @@
         <v>0.19602103531360626</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>2018</v>
       </c>
@@ -7767,7 +7780,7 @@
         <v>0.20747773349285126</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>2017</v>
       </c>
@@ -7811,7 +7824,7 @@
         <v>0.21695126593112946</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>2016</v>
       </c>
@@ -7855,7 +7868,7 @@
         <v>0.22391675412654877</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>2015</v>
       </c>
@@ -7899,7 +7912,7 @@
         <v>0.22631487250328064</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>2014</v>
       </c>
@@ -7943,7 +7956,7 @@
         <v>0.23363189399242401</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>2013</v>
       </c>
@@ -7987,7 +8000,7 @@
         <v>0.23988360166549683</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>2012</v>
       </c>
@@ -8031,7 +8044,7 @@
         <v>0.24267652630805969</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>2011</v>
       </c>
@@ -8083,9 +8096,9 @@
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1300-000000000000}">
   <dimension ref="A1:D12"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -8099,7 +8112,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>2021</v>
       </c>
@@ -8113,7 +8126,7 @@
         <v>1063.0989990234375</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>2020</v>
       </c>
@@ -8127,7 +8140,7 @@
         <v>1136.6270751953125</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>2019</v>
       </c>
@@ -8141,7 +8154,7 @@
         <v>1203.945068359375</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>2018</v>
       </c>
@@ -8155,7 +8168,7 @@
         <v>1225.0164794921875</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>2017</v>
       </c>
@@ -8169,7 +8182,7 @@
         <v>1278.19287109375</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>2016</v>
       </c>
@@ -8183,7 +8196,7 @@
         <v>1277.0340576171875</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>2015</v>
       </c>
@@ -8197,7 +8210,7 @@
         <v>1289.043212890625</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>2014</v>
       </c>
@@ -8211,7 +8224,7 @@
         <v>1242.27197265625</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>2013</v>
       </c>
@@ -8225,7 +8238,7 @@
         <v>1241.5758056640625</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>2012</v>
       </c>
@@ -8239,7 +8252,7 @@
         <v>1244.845703125</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>2011</v>
       </c>
@@ -8261,9 +8274,9 @@
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1400-000000000000}">
   <dimension ref="A1:B12"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -8271,7 +8284,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>2021</v>
       </c>
@@ -8279,7 +8292,7 @@
         <v>0.74444806575775146</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>2020</v>
       </c>
@@ -8287,7 +8300,7 @@
         <v>0.73529940843582153</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>2019</v>
       </c>
@@ -8295,7 +8308,7 @@
         <v>0.71969527006149292</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>2018</v>
       </c>
@@ -8303,7 +8316,7 @@
         <v>0.71644723415374756</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>2017</v>
       </c>
@@ -8311,7 +8324,7 @@
         <v>0.70578479766845703</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>2016</v>
       </c>
@@ -8319,7 +8332,7 @@
         <v>0.69841200113296509</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>2015</v>
       </c>
@@ -8327,7 +8340,7 @@
         <v>0.6969149112701416</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>2014</v>
       </c>
@@ -8335,7 +8348,7 @@
         <v>0.6848827600479126</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>2013</v>
       </c>
@@ -8343,7 +8356,7 @@
         <v>0.67604237794876099</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>2012</v>
       </c>
@@ -8351,7 +8364,7 @@
         <v>0.67505174875259399</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>2011</v>
       </c>
@@ -8367,9 +8380,9 @@
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1500-000000000000}">
   <dimension ref="A1:G12"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -8392,7 +8405,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>2021</v>
       </c>
@@ -8415,7 +8428,7 @@
         <v>15010.4736328125</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>2020</v>
       </c>
@@ -8438,7 +8451,7 @@
         <v>13630.5458984375</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>2019</v>
       </c>
@@ -8461,7 +8474,7 @@
         <v>13426.4130859375</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>2018</v>
       </c>
@@ -8484,7 +8497,7 @@
         <v>13551.412109375</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>2017</v>
       </c>
@@ -8507,7 +8520,7 @@
         <v>13288.7119140625</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>2016</v>
       </c>
@@ -8530,7 +8543,7 @@
         <v>13027.93359375</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>2015</v>
       </c>
@@ -8553,7 +8566,7 @@
         <v>12551.005859375</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>2014</v>
       </c>
@@ -8576,7 +8589,7 @@
         <v>12472.64453125</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>2013</v>
       </c>
@@ -8599,7 +8612,7 @@
         <v>11772.123046875</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>2012</v>
       </c>
@@ -8622,7 +8635,7 @@
         <v>11447.9716796875</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>2011</v>
       </c>
@@ -8653,9 +8666,9 @@
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1600-000000000000}">
   <dimension ref="A1:G12"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -8678,7 +8691,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>2021</v>
       </c>
@@ -8701,7 +8714,7 @@
         <v>12.490177154541016</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>2020</v>
       </c>
@@ -8724,7 +8737,7 @@
         <v>10.180279731750488</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>2019</v>
       </c>
@@ -8747,7 +8760,7 @@
         <v>10.054390907287598</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>2018</v>
       </c>
@@ -8770,7 +8783,7 @@
         <v>10.298857688903809</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>2017</v>
       </c>
@@ -8793,7 +8806,7 @@
         <v>9.6951789855957031</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>2016</v>
       </c>
@@ -8816,7 +8829,7 @@
         <v>9.6292133331298828</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>2015</v>
       </c>
@@ -8839,7 +8852,7 @@
         <v>8.9522809982299805</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>2014</v>
       </c>
@@ -8862,7 +8875,7 @@
         <v>9.6103630065917969</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>2013</v>
       </c>
@@ -8885,7 +8898,7 @@
         <v>8.5316877365112305</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>2012</v>
       </c>
@@ -8908,7 +8921,7 @@
         <v>8.4873552322387695</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>2011</v>
       </c>
@@ -8939,9 +8952,9 @@
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1700-000000000000}">
   <dimension ref="A1:I12"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -8970,12 +8983,12 @@
         <v>223</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>2021</v>
       </c>
       <c r="B2" s="1">
-        <v>37.473281860351562</v>
+        <v>37.473281860351563</v>
       </c>
       <c r="C2" s="1">
         <v>33.161907196044922</v>
@@ -8999,7 +9012,7 @@
         <v>30.396030426025391</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>2020</v>
       </c>
@@ -9028,7 +9041,7 @@
         <v>30.731967926025391</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>2019</v>
       </c>
@@ -9057,7 +9070,7 @@
         <v>30.971673965454102</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>2018</v>
       </c>
@@ -9086,7 +9099,7 @@
         <v>31.144569396972656</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>2017</v>
       </c>
@@ -9115,7 +9128,7 @@
         <v>31.52375602722168</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>2016</v>
       </c>
@@ -9144,7 +9157,7 @@
         <v>31.389076232910156</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>2015</v>
       </c>
@@ -9173,7 +9186,7 @@
         <v>31.477273941040039</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>2014</v>
       </c>
@@ -9202,7 +9215,7 @@
         <v>30.671175003051758</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>2013</v>
       </c>
@@ -9231,7 +9244,7 @@
         <v>31.733686447143555</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>2012</v>
       </c>
@@ -9239,7 +9252,7 @@
         <v>40.931427001953125</v>
       </c>
       <c r="C11" s="1">
-        <v>34.631790161132812</v>
+        <v>34.631790161132813</v>
       </c>
       <c r="D11" s="1">
         <v>40.960983276367188</v>
@@ -9260,7 +9273,7 @@
         <v>31.404634475708008</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>2011</v>
       </c>
@@ -9297,9 +9310,9 @@
 <file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1800-000000000000}">
   <dimension ref="A1:C12"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -9310,7 +9323,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>2021</v>
       </c>
@@ -9321,7 +9334,7 @@
         <v>30.396030426025391</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>2020</v>
       </c>
@@ -9332,7 +9345,7 @@
         <v>30.731967926025391</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>2019</v>
       </c>
@@ -9343,7 +9356,7 @@
         <v>30.971673965454102</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>2018</v>
       </c>
@@ -9354,7 +9367,7 @@
         <v>31.144569396972656</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>2017</v>
       </c>
@@ -9365,7 +9378,7 @@
         <v>31.52375602722168</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>2016</v>
       </c>
@@ -9376,7 +9389,7 @@
         <v>31.389076232910156</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>2015</v>
       </c>
@@ -9387,7 +9400,7 @@
         <v>31.477273941040039</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>2014</v>
       </c>
@@ -9398,7 +9411,7 @@
         <v>30.671175003051758</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>2013</v>
       </c>
@@ -9409,7 +9422,7 @@
         <v>31.733686447143555</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>2012</v>
       </c>
@@ -9420,7 +9433,7 @@
         <v>31.404634475708008</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>2011</v>
       </c>
@@ -9439,12 +9452,12 @@
 <file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6110EFEF-5A01-4DCE-A763-CA975C41B28B}">
   <dimension ref="A1:S13"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="16384" width="9.1640625" style="2"/>
+    <col min="1" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -9503,7 +9516,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A2" s="3">
         <v>2022</v>
       </c>
@@ -9562,7 +9575,7 @@
         <v>5.5216762931784897</v>
       </c>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
         <v>2021</v>
       </c>
@@ -9621,7 +9634,7 @@
         <v>5.6706813648229328</v>
       </c>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" s="3">
         <v>2020</v>
       </c>
@@ -9680,7 +9693,7 @@
         <v>5.659220700227019</v>
       </c>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
         <v>2019</v>
       </c>
@@ -9739,7 +9752,7 @@
         <v>5.4820374721529914</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="3">
         <v>2018</v>
       </c>
@@ -9798,7 +9811,7 @@
         <v>5.5945908998065192</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" s="3">
         <v>2017</v>
       </c>
@@ -9857,7 +9870,7 @@
         <v>5.4576808937696262</v>
       </c>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A8" s="3">
         <v>2016</v>
       </c>
@@ -9916,7 +9929,7 @@
         <v>5.525797385452389</v>
       </c>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A9" s="3">
         <v>2015</v>
       </c>
@@ -9975,7 +9988,7 @@
         <v>5.5649840715378822</v>
       </c>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A10" s="3">
         <v>2014</v>
       </c>
@@ -10034,7 +10047,7 @@
         <v>5.3903643381577249</v>
       </c>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A11" s="3">
         <v>2013</v>
       </c>
@@ -10093,7 +10106,7 @@
         <v>5.274529490219324</v>
       </c>
     </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A12" s="3">
         <v>2012</v>
       </c>
@@ -10152,7 +10165,7 @@
         <v>5.3171145739591719</v>
       </c>
     </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A13" s="3">
         <v>2011</v>
       </c>
@@ -10219,12 +10232,12 @@
 <file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1EDB3B34-E005-4C87-B8C9-18F31BE8EBDE}">
   <dimension ref="A1:S13"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="16384" width="9.1640625" style="2"/>
+    <col min="1" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -10283,7 +10296,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A2" s="3">
         <v>2022</v>
       </c>
@@ -10342,7 +10355,7 @@
         <v>52.209875546611748</v>
       </c>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
         <v>2021</v>
       </c>
@@ -10401,7 +10414,7 @@
         <v>52.971874522853781</v>
       </c>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" s="3">
         <v>2020</v>
       </c>
@@ -10460,7 +10473,7 @@
         <v>52.607787299207757</v>
       </c>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
         <v>2019</v>
       </c>
@@ -10519,7 +10532,7 @@
         <v>52.270196693878312</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="3">
         <v>2018</v>
       </c>
@@ -10578,7 +10591,7 @@
         <v>52.2509479274391</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" s="3">
         <v>2017</v>
       </c>
@@ -10637,7 +10650,7 @@
         <v>52.871498867811447</v>
       </c>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A8" s="3">
         <v>2016</v>
       </c>
@@ -10696,7 +10709,7 @@
         <v>52.317513309095908</v>
       </c>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A9" s="3">
         <v>2015</v>
       </c>
@@ -10755,7 +10768,7 @@
         <v>52.835801726962899</v>
       </c>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A10" s="3">
         <v>2014</v>
       </c>
@@ -10814,7 +10827,7 @@
         <v>52.859142460492649</v>
       </c>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A11" s="3">
         <v>2013</v>
       </c>
@@ -10873,7 +10886,7 @@
         <v>53.680865849140467</v>
       </c>
     </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A12" s="3">
         <v>2012</v>
       </c>
@@ -10932,7 +10945,7 @@
         <v>53.278209520200839</v>
       </c>
     </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A13" s="3">
         <v>2011</v>
       </c>
@@ -10999,12 +11012,12 @@
 <file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4DC31E3-0F92-41AC-A9AE-B4DDD81986B7}">
   <dimension ref="A1:S13"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="16384" width="9.1640625" style="2"/>
+    <col min="1" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -11063,7 +11076,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A2" s="3">
         <v>2022</v>
       </c>
@@ -11122,7 +11135,7 @@
         <v>40.600546266142317</v>
       </c>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
         <v>2021</v>
       </c>
@@ -11181,7 +11194,7 @@
         <v>41.054562072107608</v>
       </c>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" s="3">
         <v>2020</v>
       </c>
@@ -11240,7 +11253,7 @@
         <v>39.843760440890513</v>
       </c>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
         <v>2019</v>
       </c>
@@ -11299,7 +11312,7 @@
         <v>40.319883172604648</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="3">
         <v>2018</v>
       </c>
@@ -11358,7 +11371,7 @@
         <v>40.266696849462868</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" s="3">
         <v>2017</v>
       </c>
@@ -11417,7 +11430,7 @@
         <v>39.418748960193533</v>
       </c>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A8" s="3">
         <v>2016</v>
       </c>
@@ -11476,7 +11489,7 @@
         <v>39.84915810191756</v>
       </c>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A9" s="3">
         <v>2015</v>
       </c>
@@ -11535,7 +11548,7 @@
         <v>39.352172199681789</v>
       </c>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A10" s="3">
         <v>2014</v>
       </c>
@@ -11594,7 +11607,7 @@
         <v>39.518952871319449</v>
       </c>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A11" s="3">
         <v>2013</v>
       </c>
@@ -11653,7 +11666,7 @@
         <v>40.401702448873728</v>
       </c>
     </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A12" s="3">
         <v>2012</v>
       </c>
@@ -11712,7 +11725,7 @@
         <v>40.839599545303862</v>
       </c>
     </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A13" s="3">
         <v>2011</v>
       </c>
@@ -11769,6 +11782,131 @@
       </c>
       <c r="S13" s="3">
         <v>40.297658061501579</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8BA5D5A4-977D-4FE5-8DB9-A6E3FDC8A2F2}">
+  <dimension ref="A1:B14"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="16384" width="9.140625" style="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="5">
+        <v>2023</v>
+      </c>
+      <c r="B2" s="5">
+        <v>0.1272435188293457</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" s="5">
+        <v>2022</v>
+      </c>
+      <c r="B3" s="5">
+        <v>0.11270447075366974</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" s="5">
+        <v>2021</v>
+      </c>
+      <c r="B4" s="5">
+        <v>0.10624287277460098</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" s="5">
+        <v>2020</v>
+      </c>
+      <c r="B5" s="5">
+        <v>9.0409286320209503E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="5">
+        <v>2019</v>
+      </c>
+      <c r="B6" s="5">
+        <v>5.1997378468513489E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="5">
+        <v>2018</v>
+      </c>
+      <c r="B7" s="5">
+        <v>3.2197948545217514E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="5">
+        <v>2017</v>
+      </c>
+      <c r="B8" s="5">
+        <v>2.1947825327515602E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" s="5">
+        <v>2016</v>
+      </c>
+      <c r="B9" s="5">
+        <v>1.9347473978996277E-2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" s="5">
+        <v>2015</v>
+      </c>
+      <c r="B10" s="5">
+        <v>8.4177916869521141E-3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" s="5">
+        <v>2014</v>
+      </c>
+      <c r="B11" s="5">
+        <v>5.8321584947407246E-3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" s="5">
+        <v>2013</v>
+      </c>
+      <c r="B12" s="5">
+        <v>6.7878852132707834E-4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" s="5">
+        <v>2012</v>
+      </c>
+      <c r="B13" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" s="5">
+        <v>2011</v>
+      </c>
+      <c r="B14" s="5">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -11779,9 +11917,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:D12"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -11795,7 +11933,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>2021</v>
       </c>
@@ -11809,7 +11947,7 @@
         <v>0.16842389106750488</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>2020</v>
       </c>
@@ -11823,7 +11961,7 @@
         <v>0.17720137536525726</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>2019</v>
       </c>
@@ -11837,7 +11975,7 @@
         <v>0.19609326124191284</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>2018</v>
       </c>
@@ -11851,7 +11989,7 @@
         <v>0.20097571611404419</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>2017</v>
       </c>
@@ -11865,7 +12003,7 @@
         <v>0.20927385985851288</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>2016</v>
       </c>
@@ -11879,7 +12017,7 @@
         <v>0.21613813936710358</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>2015</v>
       </c>
@@ -11893,7 +12031,7 @@
         <v>0.22713750600814819</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>2014</v>
       </c>
@@ -11907,7 +12045,7 @@
         <v>0.23976245522499084</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>2013</v>
       </c>
@@ -11921,7 +12059,7 @@
         <v>0.24563494324684143</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>2012</v>
       </c>
@@ -11935,7 +12073,7 @@
         <v>0.25425693392753601</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>2011</v>
       </c>
@@ -11947,6 +12085,131 @@
       </c>
       <c r="D12" s="1">
         <v>0.26267322897911072</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B0009F3-35A3-4BFC-9468-FB9399A8B2D4}">
+  <dimension ref="A1:B14"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="16384" width="9.140625" style="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="5">
+        <v>2023</v>
+      </c>
+      <c r="B2" s="5">
+        <v>0.38649681210517883</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" s="5">
+        <v>2022</v>
+      </c>
+      <c r="B3" s="5">
+        <v>0.40734919905662537</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" s="5">
+        <v>2021</v>
+      </c>
+      <c r="B4" s="5">
+        <v>0.42366430163383484</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" s="5">
+        <v>2020</v>
+      </c>
+      <c r="B5" s="5">
+        <v>0.44781222939491272</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="5">
+        <v>2019</v>
+      </c>
+      <c r="B6" s="5">
+        <v>0.50546228885650635</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="5">
+        <v>2018</v>
+      </c>
+      <c r="B7" s="5">
+        <v>0.5472569465637207</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="5">
+        <v>2017</v>
+      </c>
+      <c r="B8" s="5">
+        <v>0.56209373474121094</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" s="5">
+        <v>2016</v>
+      </c>
+      <c r="B9" s="5">
+        <v>0.58581244945526123</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" s="5">
+        <v>2015</v>
+      </c>
+      <c r="B10" s="5">
+        <v>0.60821080207824707</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" s="5">
+        <v>2014</v>
+      </c>
+      <c r="B11" s="5">
+        <v>0.60655742883682251</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" s="5">
+        <v>2013</v>
+      </c>
+      <c r="B12" s="5">
+        <v>0.61752325296401978</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" s="5">
+        <v>2012</v>
+      </c>
+      <c r="B13" s="5">
+        <v>0.66056007146835327</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" s="5">
+        <v>2011</v>
+      </c>
+      <c r="B14" s="5">
+        <v>0.65624016523361206</v>
       </c>
     </row>
   </sheetData>
@@ -11957,9 +12220,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:D12"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -11973,7 +12236,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>2021</v>
       </c>
@@ -11987,7 +12250,7 @@
         <v>0.3706672191619873</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>2020</v>
       </c>
@@ -12001,7 +12264,7 @@
         <v>0.36530822515487671</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>2019</v>
       </c>
@@ -12015,7 +12278,7 @@
         <v>0.35292819142341614</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>2018</v>
       </c>
@@ -12029,7 +12292,7 @@
         <v>0.34467443823814392</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>2017</v>
       </c>
@@ -12043,7 +12306,7 @@
         <v>0.33777070045471191</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>2016</v>
       </c>
@@ -12057,7 +12320,7 @@
         <v>0.32983243465423584</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>2015</v>
       </c>
@@ -12071,7 +12334,7 @@
         <v>0.32803830504417419</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>2014</v>
       </c>
@@ -12085,7 +12348,7 @@
         <v>0.32248449325561523</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>2013</v>
       </c>
@@ -12099,7 +12362,7 @@
         <v>0.31972920894622803</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>2012</v>
       </c>
@@ -12113,7 +12376,7 @@
         <v>0.32425194978713989</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>2011</v>
       </c>
@@ -12135,9 +12398,9 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:Y12"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -12214,7 +12477,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>2021</v>
       </c>
@@ -12291,7 +12554,7 @@
         <v>0.47671014070510864</v>
       </c>
     </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>2020</v>
       </c>
@@ -12368,7 +12631,7 @@
         <v>0.50308620929718018</v>
       </c>
     </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>2019</v>
       </c>
@@ -12445,7 +12708,7 @@
         <v>0.553871750831604</v>
       </c>
     </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>2018</v>
       </c>
@@ -12522,7 +12785,7 @@
         <v>0.57259857654571533</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>2017</v>
       </c>
@@ -12599,7 +12862,7 @@
         <v>0.57459992170333862</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>2016</v>
       </c>
@@ -12676,7 +12939,7 @@
         <v>0.60282957553863525</v>
       </c>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>2015</v>
       </c>
@@ -12753,7 +13016,7 @@
         <v>0.62660455703735352</v>
       </c>
     </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>2014</v>
       </c>
@@ -12830,7 +13093,7 @@
         <v>0.65761297941207886</v>
       </c>
     </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>2013</v>
       </c>
@@ -12907,7 +13170,7 @@
         <v>0.67381381988525391</v>
       </c>
     </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>2012</v>
       </c>
@@ -12984,7 +13247,7 @@
         <v>0.6832919716835022</v>
       </c>
     </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>2011</v>
       </c>
@@ -13069,9 +13332,9 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:AK12"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -13184,7 +13447,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="2" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>2021</v>
       </c>
@@ -13297,7 +13560,7 @@
         <v>0.35573786497116089</v>
       </c>
     </row>
-    <row r="3" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>2020</v>
       </c>
@@ -13410,7 +13673,7 @@
         <v>0.36879754066467285</v>
       </c>
     </row>
-    <row r="4" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>2019</v>
       </c>
@@ -13523,7 +13786,7 @@
         <v>0.40687334537506104</v>
       </c>
     </row>
-    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>2018</v>
       </c>
@@ -13636,7 +13899,7 @@
         <v>0.40988072752952576</v>
       </c>
     </row>
-    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>2017</v>
       </c>
@@ -13749,7 +14012,7 @@
         <v>0.42399391531944275</v>
       </c>
     </row>
-    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>2016</v>
       </c>
@@ -13862,7 +14125,7 @@
         <v>0.42637631297111511</v>
       </c>
     </row>
-    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>2015</v>
       </c>
@@ -13975,7 +14238,7 @@
         <v>0.44104993343353271</v>
       </c>
     </row>
-    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>2014</v>
       </c>
@@ -14088,7 +14351,7 @@
         <v>0.46159008145332336</v>
       </c>
     </row>
-    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>2013</v>
       </c>
@@ -14201,7 +14464,7 @@
         <v>0.46168887615203857</v>
       </c>
     </row>
-    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>2012</v>
       </c>
@@ -14314,7 +14577,7 @@
         <v>0.4786408543586731</v>
       </c>
     </row>
-    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>2011</v>
       </c>
@@ -14435,9 +14698,9 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:N12"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -14481,7 +14744,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>2021</v>
       </c>
@@ -14525,7 +14788,7 @@
         <v>0.45434626936912537</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>2020</v>
       </c>
@@ -14569,7 +14832,7 @@
         <v>0.4524708092212677</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>2019</v>
       </c>
@@ -14613,7 +14876,7 @@
         <v>0.46188709139823914</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>2018</v>
       </c>
@@ -14657,7 +14920,7 @@
         <v>0.46009814739227295</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>2017</v>
       </c>
@@ -14701,7 +14964,7 @@
         <v>0.46906688809394836</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>2016</v>
       </c>
@@ -14745,7 +15008,7 @@
         <v>0.46952220797538757</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>2015</v>
       </c>
@@ -14789,7 +15052,7 @@
         <v>0.47507753968238831</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>2014</v>
       </c>
@@ -14833,7 +15096,7 @@
         <v>0.47185224294662476</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>2013</v>
       </c>
@@ -14877,7 +15140,7 @@
         <v>0.46994662284851074</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>2012</v>
       </c>
@@ -14921,7 +15184,7 @@
         <v>0.47699812054634094</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>2011</v>
       </c>
@@ -14973,9 +15236,9 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:C12"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -14986,7 +15249,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>2021</v>
       </c>
@@ -14997,7 +15260,7 @@
         <v>3.5066593438386917E-2</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>2020</v>
       </c>
@@ -15008,7 +15271,7 @@
         <v>3.5003498196601868E-2</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>2019</v>
       </c>
@@ -15019,7 +15282,7 @@
         <v>3.7785321474075317E-2</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>2018</v>
       </c>
@@ -15030,7 +15293,7 @@
         <v>3.5598892718553543E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>2017</v>
       </c>
@@ -15041,7 +15304,7 @@
         <v>3.7443093955516815E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>2016</v>
       </c>
@@ -15052,7 +15315,7 @@
         <v>3.3980205655097961E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>2015</v>
       </c>
@@ -15063,7 +15326,7 @@
         <v>3.2305393368005753E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>2014</v>
       </c>
@@ -15074,7 +15337,7 @@
         <v>3.4291055053472519E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>2013</v>
       </c>
@@ -15085,7 +15348,7 @@
         <v>3.6509472876787186E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>2012</v>
       </c>
@@ -15096,7 +15359,7 @@
         <v>3.7717249244451523E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>2011</v>
       </c>
@@ -15115,9 +15378,9 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:G12"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -15140,7 +15403,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>2021</v>
       </c>
@@ -15163,7 +15426,7 @@
         <v>9.5635483739897609E-4</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>2020</v>
       </c>
@@ -15186,7 +15449,7 @@
         <v>1.4260361203923821E-3</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>2019</v>
       </c>
@@ -15209,7 +15472,7 @@
         <v>3.5407401155680418E-3</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>2018</v>
       </c>
@@ -15232,7 +15495,7 @@
         <v>2.6370126288384199E-3</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>2017</v>
       </c>
@@ -15255,7 +15518,7 @@
         <v>3.3703474327921867E-3</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>2016</v>
       </c>
@@ -15278,7 +15541,7 @@
         <v>3.2672595698386431E-3</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>2015</v>
       </c>
@@ -15301,7 +15564,7 @@
         <v>1.5344700077548623E-3</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>2014</v>
       </c>
@@ -15324,7 +15587,7 @@
         <v>3.6169742234051228E-3</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>2013</v>
       </c>
@@ -15347,7 +15610,7 @@
         <v>5.6807822547852993E-3</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>2012</v>
       </c>
@@ -15370,7 +15633,7 @@
         <v>4.1426578536629677E-3</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>2011</v>
       </c>
